--- a/output/upload/S00022_2259_바로연금보험_무배당.xlsx
+++ b/output/upload/S00022_2259_바로연금보험_무배당.xlsx
@@ -1372,11 +1372,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1416,11 +1436,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1460,11 +1500,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1504,11 +1564,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1548,11 +1628,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1592,11 +1692,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1636,11 +1756,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1680,11 +1820,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1724,11 +1884,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1768,11 +1948,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1812,11 +2012,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1856,11 +2076,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1900,11 +2140,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1944,11 +2204,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1988,11 +2268,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2032,11 +2332,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2076,11 +2396,31 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2120,11 +2460,31 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2164,11 +2524,31 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2208,11 +2588,31 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2252,11 +2652,31 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2296,11 +2716,31 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2340,11 +2780,31 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2384,11 +2844,31 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2428,11 +2908,31 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2472,11 +2972,31 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2515,8 +3035,31 @@
       <c r="AD32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2534,8 +3077,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2553,8 +3119,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2572,8 +3161,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2591,8 +3203,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2610,8 +3245,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2629,8 +3287,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2648,8 +3329,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2667,8 +3371,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2686,8 +3413,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2705,8 +3455,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2724,8 +3497,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2743,8 +3539,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2762,8 +3581,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2781,8 +3623,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00022_2259_바로연금보험_무배당.xlsx
+++ b/output/upload/S00022_2259_바로연금보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD47"/>
+  <dimension ref="A1:AD32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259851</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)적립</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1502,22 +1502,22 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259802</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259802</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1566,22 +1566,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259802</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259852</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)적립</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1630,22 +1630,22 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259803</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259803</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1694,22 +1694,22 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259803</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259853</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)적립</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1758,22 +1758,22 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259804</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259804</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1822,22 +1822,22 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259804</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259854</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)적립</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1886,22 +1886,22 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259805</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259805</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1950,22 +1950,22 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259805</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259855</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)적립</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2014,22 +2014,22 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259806</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259806</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2078,22 +2078,22 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259806</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259856</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)적립</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2142,22 +2142,22 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259807</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259807</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2206,22 +2206,22 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259807</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259857</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)적립</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2270,22 +2270,22 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259808</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259808</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2334,22 +2334,22 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259808</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259858</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)적립</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2398,22 +2398,22 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259809</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259809</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2462,22 +2462,22 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259809</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259859</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)적립</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2526,22 +2526,22 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259810</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259810</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2590,22 +2590,22 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259810</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259860</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)적립</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2654,22 +2654,22 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259811</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259811</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2718,22 +2718,22 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259811</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>2259801</t>
+          <t>2259861</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)적립</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2780,41 +2780,13 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
@@ -2824,11 +2796,7 @@
       <c r="O29" s="6" t="n"/>
       <c r="P29" s="6" t="n"/>
       <c r="Q29" s="6" t="n"/>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R29" s="6" t="n"/>
       <c r="S29" s="6" t="n"/>
       <c r="T29" s="6" t="n"/>
       <c r="U29" s="6" t="n"/>
@@ -2844,41 +2812,13 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
@@ -2888,11 +2828,7 @@
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R30" s="6" t="n"/>
       <c r="S30" s="6" t="n"/>
       <c r="T30" s="6" t="n"/>
       <c r="U30" s="6" t="n"/>
@@ -2908,41 +2844,13 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
@@ -2952,11 +2860,7 @@
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
       <c r="Q31" s="6" t="n"/>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R31" s="6" t="n"/>
       <c r="S31" s="6" t="n"/>
       <c r="T31" s="6" t="n"/>
       <c r="U31" s="6" t="n"/>
@@ -2972,41 +2876,13 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
@@ -3016,11 +2892,7 @@
       <c r="O32" s="6" t="n"/>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R32" s="6" t="n"/>
       <c r="S32" s="6" t="n"/>
       <c r="T32" s="6" t="n"/>
       <c r="U32" s="6" t="n"/>
@@ -3034,636 +2906,6 @@
       <c r="AC32" s="6" t="n"/>
       <c r="AD32" s="6" t="n"/>
     </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2259801</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="R3:AD3"/>
